--- a/artfynd/A 21700-2024 artfynd.xlsx
+++ b/artfynd/A 21700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,72 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14673482</v>
+        <v>75734792</v>
       </c>
       <c r="B2" t="n">
-        <v>40069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102476</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Töcknig trymal</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perittia obscurepunctella</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Stainton, 1848)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
+          <t>G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älvkarleö, Norge-hygget, Upl</t>
+          <t>Norge N om Storfjärden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631448.5072221139</v>
+        <v>631256</v>
       </c>
       <c r="R2" t="n">
-        <v>6713987.929037361</v>
+        <v>6713930</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-07-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På stammen av levande ek, omkr. 452 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,29 +762,260 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövhygge</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Jan-Olov Björklund</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123938421</v>
+      </c>
+      <c r="B3" t="n">
+        <v>84147</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1444</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcoscypha coccinea s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norge, Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631250</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713947</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alf Linderheim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alf Linderheim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14673482</v>
+      </c>
+      <c r="B4" t="n">
+        <v>40774</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102476</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Töcknig trymal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perittia obscurepunctella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Stainton, 1848)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Älvkarleö, Norge-hygget, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631449</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713988</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1983-05-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1983-05-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövhygge</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
           <t>Jan-Olov Björklund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Jan-Olov Björklund</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Upplandsstiftelsen</t>
         </is>

--- a/artfynd/A 21700-2024 artfynd.xlsx
+++ b/artfynd/A 21700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75734792</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123938421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
           <t>Upplandsstiftelsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14673482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>